--- a/DataTables/Datas/buff.xlsx
+++ b/DataTables/Datas/buff.xlsx
@@ -477,6 +477,11 @@
           <t>param1</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>##备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,10 +563,6 @@
           <t>1战斗内显示2背包显示</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>1抗臭2易伤3回合结束随机造成伤害</t>
@@ -582,22 +583,6 @@
           <t>2易伤倍数3伤害次数</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
